--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -871,7 +871,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 18:16:53</t>
+          <t>2026-09-13 20:12:36</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 19:38:25</t>
+          <t>2026-09-13 20:32:00</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:44:55</t>
+          <t>2026-09-13 20:43:42</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:55:12</t>
+          <t>2026-09-13 20:50:48</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 14:44:40</t>
+          <t>2026-09-13 21:05:54</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 15:15:41</t>
+          <t>2026-09-13 21:29:38</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1075,6 +1075,41 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:19:21</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-11收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1110,6 +1110,41 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14 19:17:25</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-14收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 22:19:21</t>
+          <t>2026-09-14 20:29:49</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>对2026-09-11收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+          <t>对2026-09-14收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1105,41 +1105,6 @@
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>通过规则引擎校验后写入决策记录/交易账本</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-14 19:17:25</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>对2026-09-14收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>无操作信号</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>通过规则引擎校验后写入决策记录/交易账本</t>
         </is>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1110,6 +1110,41 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15 18:44:25</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-15收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1145,6 +1145,41 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15 19:57:09</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-15收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1180,6 +1180,41 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15 21:22:25</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-15收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1215,6 +1215,41 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15 21:43:18</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-15收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1250,6 +1250,41 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16 18:31:48</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-16收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1285,6 +1285,41 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16 19:53:16</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-16收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1250,76 +1250,6 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16 18:31:48</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>对2026-09-16收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>无操作信号</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>通过规则引擎校验后写入决策记录/交易账本</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16 19:53:16</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>对2026-09-16收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>无操作信号</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>通过规则引擎校验后写入决策记录/交易账本</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1250,6 +1250,41 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17 18:41:29</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-17收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号；拦截1笔</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1285,6 +1285,41 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17 19:56:50</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-17收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号；拦截1笔</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 18:41:29</t>
+          <t>2026-09-17 20:18:54</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>无操作信号；拦截1笔</t>
+          <t>生成1条决策：卖出紫金矿业(601899)；拦截1笔</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1280,41 +1280,6 @@
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>通过规则引擎校验后写入决策记录/交易账本</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-17 19:56:50</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>对2026-09-17收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>无操作信号；拦截1笔</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>通过规则引擎校验后写入决策记录/交易账本</t>
         </is>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1285,6 +1285,41 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:17:09</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-18收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>生成1条决策：买入紫金矿业(601899)</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -1291,7 +1291,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 18:17:09</t>
+          <t>2026-09-18 21:06:23</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1320,6 +1320,41 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21 19:31:05</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-21收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1355,6 +1355,41 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21 21:07:33</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-21收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1390,6 +1390,41 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:00:49</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-21收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1425,6 +1425,41 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:12:21</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-21收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1460,6 +1460,41 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22 18:37:31</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-22收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1495,6 +1495,41 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22 19:55:41</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-22收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1530,6 +1530,41 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22 21:17:39</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-22收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1565,6 +1565,41 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22 21:31:24</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-22收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1600,6 +1600,41 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23 18:33:36</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-23收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1635,6 +1635,41 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:55:32</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-23收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1670,6 +1670,41 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23 21:32:17</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-23收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1705,6 +1705,41 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23 21:46:20</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-23收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1740,6 +1740,41 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 18:47:08</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-24收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1775,6 +1775,41 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 20:02:36</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-24收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1810,6 +1810,41 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:28:22</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-24收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1845,6 +1845,41 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 21:40:36</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-24收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1880,6 +1880,41 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 18:56:18</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-24收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1915,6 +1915,41 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 20:05:39</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-24收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1950,6 +1950,41 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 21:34:32</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-24收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1985,6 +1985,41 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 22:05:13</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-24收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2020,6 +2020,41 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26 14:57:09</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-24收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2055,6 +2055,41 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26 15:56:11</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-24收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2090,6 +2090,41 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 20:25:27</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-28收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>生成1条决策：卖出沪深300ETF(510300)；拦截2笔</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2125,6 +2125,41 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 19:52:20</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-29收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>生成2条决策：买入紫金矿业(601899)；买入宁德时代(300750)</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2160,6 +2160,41 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 19:37:19</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-30收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2195,6 +2195,41 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 20:53:02</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-30收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2230,6 +2230,41 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 22:49:05</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-30收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2265,6 +2265,41 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 23:07:51</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-30收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2300,6 +2300,41 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01 20:09:24</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-30收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2335,6 +2335,41 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01 21:42:13</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-30收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2370,6 +2370,41 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:33:16</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-30收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2405,6 +2405,41 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02 19:41:35</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-30收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2440,6 +2440,41 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02 20:59:26</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-30收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2475,6 +2475,41 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02 22:42:38</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-30收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2510,6 +2510,41 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02 22:53:20</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-30收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2545,6 +2545,41 @@
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03 15:24:10</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-30收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2580,6 +2580,41 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03 16:25:49</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-30收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2615,6 +2615,41 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05 21:09:57</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-30收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2650,6 +2650,41 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05 23:09:26</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-30收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2685,6 +2685,41 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06 20:31:03</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-30收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2720,6 +2720,41 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06 21:32:50</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-30收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2755,6 +2755,41 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06 23:00:53</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-30收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2790,6 +2790,41 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06 23:23:20</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-30收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2825,6 +2825,41 @@
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07 20:24:23</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-30收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2860,6 +2860,41 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07 21:43:55</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-30收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2895,6 +2895,41 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07 23:29:41</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-30收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2930,6 +2930,41 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07 23:44:35</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>对2026-09-30收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2965,6 +2965,41 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08 20:30:37</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-08收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3000,6 +3000,41 @@
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08 21:48:40</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-08收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3035,6 +3035,41 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08 23:27:40</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-08收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3070,6 +3070,41 @@
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08 23:44:52</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-08收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3105,6 +3105,41 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:20:34</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-09收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3140,6 +3140,41 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09 21:33:30</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-09收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3175,6 +3175,41 @@
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09 23:10:26</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-09收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3210,6 +3210,41 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09 23:24:03</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-09收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3245,6 +3245,41 @@
         </is>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-10 15:56:22</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-09收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3280,6 +3280,41 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:42:19</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-09收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3315,6 +3315,41 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12 21:56:35</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-12收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3350,6 +3350,41 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12 23:49:54</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-12收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3385,6 +3385,41 @@
         </is>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 15:08:51</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-13收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3420,6 +3420,41 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 21:13:38</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-13收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3455,6 +3455,41 @@
         </is>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 22:27:22</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-13收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3490,6 +3490,41 @@
         </is>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 23:48:39</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-13收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3525,6 +3525,41 @@
         </is>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 18:53:44</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-14收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>生成1条决策：卖出中国平安(601318)；拦截1笔</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3560,6 +3560,41 @@
         </is>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 18:35:45</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-15收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>生成1条决策：买入长江电力(600900)</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3595,6 +3595,41 @@
         </is>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16 18:23:05</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-16收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3630,6 +3630,41 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16 19:43:18</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-16收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3665,6 +3665,41 @@
         </is>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:08:46</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-16收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3700,6 +3700,41 @@
         </is>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:22:41</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-16收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3735,6 +3735,41 @@
         </is>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17 14:26:01</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-16收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3770,6 +3770,41 @@
         </is>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17 15:05:48</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-16收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3805,6 +3805,41 @@
         </is>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19 19:38:56</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-19收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>生成1条决策：卖出宁德时代(300750)；拦截1笔</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3840,6 +3840,41 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 18:42:13</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-20收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>生成1条决策：买入美的集团(000333)</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3875,6 +3875,41 @@
         </is>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 18:54:50</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-21收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3910,6 +3910,41 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 20:07:24</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-21收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3945,6 +3945,41 @@
         </is>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 21:38:13</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-21收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3980,6 +3980,41 @@
         </is>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 21:59:13</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-21收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4015,6 +4015,41 @@
         </is>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 18:53:36</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-22收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>生成1条决策：卖出紫金矿业(601899)；拦截1笔</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4050,6 +4050,41 @@
         </is>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 18:44:42</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-23收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>生成1条决策：买入宁德时代(300750)</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4085,6 +4085,41 @@
         </is>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 19:55:20</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-26收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4120,6 +4120,41 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 21:23:38</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-26收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G106"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4155,6 +4155,41 @@
         </is>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 23:03:10</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-26收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4190,6 +4190,41 @@
         </is>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 23:19:44</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-26收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4225,6 +4225,41 @@
         </is>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 19:18:26</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-27收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4260,6 +4260,41 @@
         </is>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 20:31:50</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-27收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4295,6 +4295,41 @@
         </is>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:17:12</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-27收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G111"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4330,6 +4330,41 @@
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:05:09</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-27收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G112"/>
+  <dimension ref="A1:G113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4365,6 +4365,41 @@
         </is>
       </c>
     </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 19:52:19</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-28收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G113"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4400,6 +4400,41 @@
         </is>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 21:19:36</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-28收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4435,6 +4435,41 @@
         </is>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 23:00:25</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-28收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G115"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4470,6 +4470,41 @@
         </is>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 23:15:34</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-28收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:G117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4505,6 +4505,41 @@
         </is>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 20:00:27</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-29收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G117"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4540,6 +4540,41 @@
         </is>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 21:27:08</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-29收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:G119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4575,6 +4575,41 @@
         </is>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 23:06:35</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-29收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G119"/>
+  <dimension ref="A1:G120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4610,6 +4610,41 @@
         </is>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 23:20:30</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-29收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G120"/>
+  <dimension ref="A1:G121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4645,6 +4645,41 @@
         </is>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 19:54:48</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-30收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G121"/>
+  <dimension ref="A1:G122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4680,6 +4680,41 @@
         </is>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 21:18:21</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-30收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G122"/>
+  <dimension ref="A1:G123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4715,6 +4715,41 @@
         </is>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 22:58:19</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-30收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G123"/>
+  <dimension ref="A1:G124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4750,6 +4750,41 @@
         </is>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 23:09:18</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-30收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G124"/>
+  <dimension ref="A1:G125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4785,6 +4785,41 @@
         </is>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31 15:46:51</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-30收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/11_AI使用记录.xlsx
+++ b/outputs/11_AI使用记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G125"/>
+  <dimension ref="A1:G126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4820,6 +4820,41 @@
         </is>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31 16:35:35</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>对2026-10-30收盘数据执行选股与决策流水线：候选池评分、持仓风控、规则引擎前置校验</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>无操作信号</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>行情与财务数据来自东方财富公开接口，非AI生成数据；指标计算结果可与同花顺APP核对</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>PENDING——按config.json预设策略自动执行，待人工复盘确认</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>通过规则引擎校验后写入决策记录/交易账本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
